--- a/Pruebas calificadas/COLEGIO-SANTA-LUCIA-(IED)-701 (2)_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-SANTA-LUCIA-(IED)-701 (2)_CALIFICADO.xlsx
@@ -1111,9 +1111,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -1617,9 +1617,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2629,9 +2629,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -3641,9 +3641,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4653,9 +4653,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5159,9 +5159,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5665,9 +5665,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -6171,9 +6171,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -7681,9 +7681,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -8693,9 +8693,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -9199,9 +9199,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -10713,9 +10713,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -11219,9 +11219,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -11725,9 +11725,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -12737,9 +12737,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -13243,9 +13243,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -13749,9 +13749,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -14761,9 +14761,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -15773,9 +15773,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -16275,9 +16275,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -16781,9 +16781,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -17287,9 +17287,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -17793,9 +17793,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -18299,9 +18299,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -18805,9 +18805,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -19311,9 +19311,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -20319,9 +20319,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -20825,9 +20825,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-SANTA-LUCIA-(IED)-701 (2)_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-SANTA-LUCIA-(IED)-701 (2)_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,11 +6285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -6385,7 +6293,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,11 +6534,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -6638,7 +6542,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,11 +6783,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -6891,7 +6791,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,11 +7024,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -7136,7 +7032,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7377,11 +7273,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -7389,7 +7281,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7630,11 +7522,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -7642,7 +7530,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7883,11 +7771,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -7895,7 +7779,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8136,11 +8020,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -8148,7 +8028,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8389,11 +8269,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -8401,7 +8277,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8642,11 +8518,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -8654,7 +8526,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8895,11 +8767,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -8907,7 +8775,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9148,11 +9016,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -9160,7 +9024,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9401,11 +9265,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -9413,7 +9273,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9654,11 +9514,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -9666,7 +9522,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9903,11 +9759,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -9915,7 +9767,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10156,11 +10008,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -10168,7 +10016,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10409,11 +10257,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -10421,7 +10265,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10662,11 +10506,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -10674,7 +10514,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10915,11 +10755,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -10927,7 +10763,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11168,11 +11004,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -11180,7 +11012,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11421,11 +11253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -11433,7 +11261,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11674,11 +11502,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -11686,7 +11510,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11927,11 +11751,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -11939,7 +11759,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12180,11 +12000,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -12192,7 +12008,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12433,11 +12249,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -12445,7 +12257,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12686,11 +12498,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -12698,7 +12506,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12939,11 +12747,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -12951,7 +12755,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13192,11 +12996,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -13204,7 +13004,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13445,11 +13245,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -13457,7 +13253,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13698,11 +13494,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -13710,7 +13502,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13951,11 +13743,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -13963,7 +13751,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14204,11 +13992,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -14216,7 +14000,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14457,11 +14241,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -14469,7 +14249,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14710,11 +14490,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -14722,7 +14498,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14963,11 +14739,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -14975,7 +14747,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15216,11 +14988,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -15228,7 +14996,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15469,11 +15237,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -15481,7 +15245,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15722,11 +15486,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -15734,7 +15494,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15971,11 +15731,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -15983,7 +15739,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16224,11 +15980,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -16236,7 +15988,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16477,11 +16229,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -16489,7 +16237,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16730,11 +16478,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -16742,7 +16486,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16983,11 +16727,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -16995,7 +16735,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17236,11 +16976,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -17248,7 +16984,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17489,11 +17225,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -17501,7 +17233,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17742,11 +17474,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -17754,7 +17482,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17995,11 +17723,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -18007,7 +17731,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18248,11 +17972,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -18260,7 +17980,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18501,11 +18221,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -18513,7 +18229,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18754,11 +18470,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -18766,7 +18478,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -19007,11 +18719,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -19019,7 +18727,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19260,11 +18968,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -19272,7 +18976,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19509,11 +19213,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -19521,7 +19221,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19762,11 +19462,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -19774,7 +19470,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -20015,11 +19711,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -20027,7 +19719,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20268,11 +19960,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -20280,7 +19968,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20521,11 +20209,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -20533,7 +20217,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20774,11 +20458,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -20786,7 +20466,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -21027,11 +20707,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -21039,7 +20715,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21280,11 +20956,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001098965</t>
@@ -21292,7 +20964,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTA LUCIA (IED)</t>
+          <t>COLEGIO SANTA LUCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
